--- a/data/tags/אלבומים חדשים/sites/rotter/2026-05-week03/titles.xlsx
+++ b/data/tags/אלבומים חדשים/sites/rotter/2026-05-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>זהו זה - זהו זה 2020 עונה 5 (2023)</v>
+        <v>זהו זה - זהו זה 2020 עונה 4 (2022)</v>
       </c>
       <c r="B2" t="str">
         <v>2026-05-15</v>
       </c>
       <c r="C2" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24191&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24068&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-17</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>06:50</v>
+        <v>06:51</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,50 +469,12 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>זהו זה - זהו זה 2020 עונה 5 (2023)</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>אריק סיני - כל השירים היפים באמת</v>
-      </c>
-      <c r="B3" t="str">
-        <v>2026-05-15</v>
-      </c>
-      <c r="C3" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24470&amp;forum=music&amp;viewmode=all</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2026-05-15</v>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v>06:45</v>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v>אלבומים חדשים</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v>אריק סיני - כל השירים היפים באמת</v>
+        <v>זהו זה - זהו זה 2020 עונה 4 (2022)</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
   </ignoredErrors>
 </worksheet>
 </file>